--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SA TINTINA CB ES CASTELL MENORCA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SA TINTINA CB ES CASTELL MENORCA.xlsx
@@ -565,13 +565,13 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>96.45489999999999</v>
+        <v>112.8349</v>
       </c>
       <c r="E2" t="n">
-        <v>95.5934</v>
+        <v>106.8763</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8615000000000002</v>
+        <v>5.9585</v>
       </c>
       <c r="G2" t="n">
         <v>67.24509999999999</v>
@@ -610,13 +610,13 @@
         <v>48.0543</v>
       </c>
       <c r="S2" t="n">
-        <v>-11.7519</v>
+        <v>4.6283</v>
       </c>
       <c r="T2" t="n">
-        <v>-7.2519</v>
+        <v>4.0312</v>
       </c>
       <c r="U2" t="n">
-        <v>-4.4998</v>
+        <v>0.5972999999999998</v>
       </c>
       <c r="V2" t="n">
         <v>45.4543</v>
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>63.8665</v>
+        <v>48.2062</v>
       </c>
       <c r="E3" t="n">
-        <v>39.1696</v>
+        <v>27.8215</v>
       </c>
       <c r="F3" t="n">
-        <v>24.6971</v>
+        <v>20.3846</v>
       </c>
       <c r="G3" t="n">
         <v>9.626799999999999</v>
@@ -688,13 +688,13 @@
         <v>51.18</v>
       </c>
       <c r="S3" t="n">
-        <v>44.6553</v>
+        <v>28.9952</v>
       </c>
       <c r="T3" t="n">
-        <v>27.7632</v>
+        <v>16.4156</v>
       </c>
       <c r="U3" t="n">
-        <v>16.8918</v>
+        <v>12.5794</v>
       </c>
       <c r="V3" t="n">
         <v>9.193300000000001</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. MARKOVETSKYY</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>38.3411</v>
+        <v>42.2648</v>
       </c>
       <c r="E4" t="n">
-        <v>41.6625</v>
+        <v>37.88200000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.3216</v>
+        <v>4.382400000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3217</v>
+        <v>21.0398</v>
       </c>
       <c r="H4" t="n">
-        <v>16.3359</v>
+        <v>5.840300000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.0141</v>
+        <v>15.1992</v>
       </c>
       <c r="J4" t="n">
-        <v>23.7015</v>
+        <v>49.3152</v>
       </c>
       <c r="K4" t="n">
-        <v>21.5835</v>
+        <v>24.1129</v>
       </c>
       <c r="L4" t="n">
-        <v>2.118</v>
+        <v>25.2023</v>
       </c>
       <c r="M4" t="n">
-        <v>-10.3798</v>
+        <v>-28.2757</v>
       </c>
       <c r="N4" t="n">
-        <v>-5.2474</v>
+        <v>-18.2722</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.1323</v>
+        <v>-10.0033</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.7115</v>
+        <v>-1.5628</v>
       </c>
       <c r="Q4" t="n">
-        <v>-16.018</v>
+        <v>-47.8589</v>
       </c>
       <c r="R4" t="n">
-        <v>12.3066</v>
+        <v>46.2965</v>
       </c>
       <c r="S4" t="n">
-        <v>27.4427</v>
+        <v>8.0067</v>
       </c>
       <c r="T4" t="n">
-        <v>24.1142</v>
+        <v>6.6184</v>
       </c>
       <c r="U4" t="n">
-        <v>3.3284</v>
+        <v>1.3884</v>
       </c>
       <c r="V4" t="n">
-        <v>1.287999999999999</v>
+        <v>14.7812</v>
       </c>
       <c r="W4" t="n">
-        <v>9.864800000000001</v>
+        <v>29.8072</v>
       </c>
       <c r="X4" t="n">
-        <v>-8.576599999999999</v>
+        <v>-15.0262</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>33.0251</v>
+        <v>33.2327</v>
       </c>
       <c r="E5" t="n">
-        <v>11.7068</v>
+        <v>12.6151</v>
       </c>
       <c r="F5" t="n">
-        <v>21.3189</v>
+        <v>20.6175</v>
       </c>
       <c r="G5" t="n">
         <v>29.8904</v>
@@ -844,13 +844,13 @@
         <v>36.7245</v>
       </c>
       <c r="S5" t="n">
-        <v>12.3169</v>
+        <v>12.5243</v>
       </c>
       <c r="T5" t="n">
-        <v>5.516400000000001</v>
+        <v>6.4249</v>
       </c>
       <c r="U5" t="n">
-        <v>6.8008</v>
+        <v>6.0992</v>
       </c>
       <c r="V5" t="n">
         <v>4.8824</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>V. MARKOVETSKYY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>25.6047</v>
+        <v>24.683</v>
       </c>
       <c r="E6" t="n">
-        <v>29.3915</v>
+        <v>29.0423</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.7865</v>
+        <v>-4.359100000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>21.0398</v>
+        <v>13.3217</v>
       </c>
       <c r="H6" t="n">
-        <v>5.840300000000001</v>
+        <v>16.3359</v>
       </c>
       <c r="I6" t="n">
-        <v>15.1992</v>
+        <v>-3.0141</v>
       </c>
       <c r="J6" t="n">
-        <v>49.3152</v>
+        <v>23.7015</v>
       </c>
       <c r="K6" t="n">
-        <v>24.1129</v>
+        <v>21.5835</v>
       </c>
       <c r="L6" t="n">
-        <v>25.2023</v>
+        <v>2.118</v>
       </c>
       <c r="M6" t="n">
-        <v>-28.2757</v>
+        <v>-10.3798</v>
       </c>
       <c r="N6" t="n">
-        <v>-18.2722</v>
+        <v>-5.2474</v>
       </c>
       <c r="O6" t="n">
-        <v>-10.0033</v>
+        <v>-5.1323</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5628</v>
+        <v>-3.7115</v>
       </c>
       <c r="Q6" t="n">
-        <v>-47.8589</v>
+        <v>-16.018</v>
       </c>
       <c r="R6" t="n">
-        <v>46.2965</v>
+        <v>12.3066</v>
       </c>
       <c r="S6" t="n">
-        <v>-8.653599999999999</v>
+        <v>13.7849</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.8723</v>
+        <v>11.4942</v>
       </c>
       <c r="U6" t="n">
-        <v>-6.7811</v>
+        <v>2.2906</v>
       </c>
       <c r="V6" t="n">
-        <v>14.7812</v>
+        <v>1.287999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>29.8072</v>
+        <v>9.864800000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>-15.0262</v>
+        <v>-8.576599999999999</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>22.864</v>
+        <v>22.4631</v>
       </c>
       <c r="E7" t="n">
-        <v>7.423199999999999</v>
+        <v>8.513100000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>15.4409</v>
+        <v>13.9498</v>
       </c>
       <c r="G7" t="n">
         <v>-2.279999999999999</v>
@@ -1000,13 +1000,13 @@
         <v>42.1941</v>
       </c>
       <c r="S7" t="n">
-        <v>12.646</v>
+        <v>12.2455</v>
       </c>
       <c r="T7" t="n">
-        <v>6.3509</v>
+        <v>7.4409</v>
       </c>
       <c r="U7" t="n">
-        <v>6.2954</v>
+        <v>4.8042</v>
       </c>
       <c r="V7" t="n">
         <v>10.3492</v>
@@ -1033,13 +1033,13 @@
         <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0747</v>
+        <v>6.281700000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>4.9918</v>
+        <v>8.0853</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.9171</v>
+        <v>-1.8034</v>
       </c>
       <c r="G8" t="n">
         <v>4.366300000000001</v>
@@ -1078,13 +1078,13 @@
         <v>17.9716</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5445</v>
+        <v>2.6625</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7113999999999998</v>
+        <v>2.382</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8333999999999999</v>
+        <v>0.2805000000000002</v>
       </c>
       <c r="V8" t="n">
         <v>-12.0764</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. MAS CARDONA</t>
+          <t>V. FERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1749</v>
+        <v>1.5211</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5948</v>
+        <v>-7.2112</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7697</v>
+        <v>8.7323</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7109000000000001</v>
+        <v>4.121</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1384</v>
+        <v>-2.0411</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8492999999999999</v>
+        <v>6.162</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0417</v>
+        <v>9.798999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0013</v>
+        <v>1.8779</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0405</v>
+        <v>7.9214</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6692</v>
+        <v>-5.6782</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1397</v>
+        <v>-3.9186</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8089</v>
+        <v>-1.7595</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-5.2743</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-21.2922</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>16.018</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5514</v>
+        <v>0.9993999999999998</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5531</v>
+        <v>2.1739</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0017</v>
+        <v>-1.1746</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4372</v>
+        <v>1.675</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.1081</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4372</v>
+        <v>-0.4331999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.033599999999999</v>
+        <v>0.8759999999999994</v>
       </c>
       <c r="E10" t="n">
-        <v>6.092200000000001</v>
+        <v>5.5645</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.1257</v>
+        <v>-4.688499999999999</v>
       </c>
       <c r="G10" t="n">
         <v>2.9581</v>
@@ -1234,13 +1234,13 @@
         <v>34.5757</v>
       </c>
       <c r="S10" t="n">
-        <v>8.477600000000001</v>
+        <v>11.3871</v>
       </c>
       <c r="T10" t="n">
-        <v>7.6002</v>
+        <v>7.0723</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8778000000000001</v>
+        <v>4.3146</v>
       </c>
       <c r="V10" t="n">
         <v>-8.9765</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. TALTAVULL BALLE</t>
+          <t>O. MAS CARDONA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7158</v>
+        <v>-1.3088</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1364</v>
+        <v>0.352</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5794</v>
+        <v>-1.6608</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2712</v>
+        <v>0.7109000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5464</v>
+        <v>-0.1384</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.8177</v>
+        <v>0.8492999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.8505</v>
+        <v>0.0417</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0451</v>
+        <v>0.0013</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.8956</v>
+        <v>0.0405</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5791999999999999</v>
+        <v>0.6692</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4985999999999999</v>
+        <v>-0.1397</v>
       </c>
       <c r="O11" t="n">
-        <v>1.078</v>
+        <v>0.8089</v>
       </c>
       <c r="P11" t="n">
-        <v>2.9301</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9301</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6519</v>
+        <v>0.4175</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2858999999999999</v>
+        <v>0.3103</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.366</v>
+        <v>0.1073</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.7229</v>
+        <v>-2.4372</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.7229</v>
+        <v>-2.4372</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. NDOYE</t>
+          <t>P. TALTAVULL BALLE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0749</v>
+        <v>-3.3225</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.926499999999999</v>
+        <v>-3.0154</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8514</v>
+        <v>-0.3071000000000002</v>
       </c>
       <c r="G12" t="n">
-        <v>-9.7758</v>
+        <v>-2.2712</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.6923</v>
+        <v>0.5464</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.0835</v>
+        <v>-2.8177</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3506</v>
+        <v>-2.8505</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1646999999999994</v>
+        <v>1.0451</v>
       </c>
       <c r="L12" t="n">
-        <v>2.1862</v>
+        <v>-3.8956</v>
       </c>
       <c r="M12" t="n">
-        <v>-12.1262</v>
+        <v>0.5791999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.8568</v>
+        <v>-0.4985999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.2695</v>
+        <v>1.078</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.664800000000001</v>
+        <v>2.9301</v>
       </c>
       <c r="Q12" t="n">
-        <v>-28.7153</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>23.0506</v>
+        <v>2.9301</v>
       </c>
       <c r="S12" t="n">
-        <v>8.0661</v>
+        <v>-0.2584</v>
       </c>
       <c r="T12" t="n">
-        <v>4.9761</v>
+        <v>-0.1648999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>3.0899</v>
+        <v>-0.09380000000000002</v>
       </c>
       <c r="V12" t="n">
-        <v>3.2996</v>
+        <v>-3.7229</v>
       </c>
       <c r="W12" t="n">
-        <v>14.4617</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-11.1623</v>
+        <v>-3.7229</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ RODRIGUEZ</t>
+          <t>S. NDOYE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.6059</v>
+        <v>-6.673999999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.9429</v>
+        <v>-8.908999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>6.337</v>
+        <v>2.2345</v>
       </c>
       <c r="G13" t="n">
-        <v>4.121</v>
+        <v>-9.7758</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.0411</v>
+        <v>-6.6923</v>
       </c>
       <c r="I13" t="n">
-        <v>6.162</v>
+        <v>-3.0835</v>
       </c>
       <c r="J13" t="n">
-        <v>9.798999999999999</v>
+        <v>2.3506</v>
       </c>
       <c r="K13" t="n">
-        <v>1.8779</v>
+        <v>0.1646999999999994</v>
       </c>
       <c r="L13" t="n">
-        <v>7.9214</v>
+        <v>2.1862</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.6782</v>
+        <v>-12.1262</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.9186</v>
+        <v>-6.8568</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.7595</v>
+        <v>-5.2695</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.2743</v>
+        <v>-5.664800000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-21.2922</v>
+        <v>-28.7153</v>
       </c>
       <c r="R13" t="n">
-        <v>16.018</v>
+        <v>23.0506</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.127800000000001</v>
+        <v>5.466699999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.5577</v>
+        <v>2.9938</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.5697</v>
+        <v>2.4731</v>
       </c>
       <c r="V13" t="n">
-        <v>1.675</v>
+        <v>3.2996</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1081</v>
+        <v>14.4617</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4331999999999999</v>
+        <v>-11.1623</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>-39.6015</v>
+        <v>-28.896</v>
       </c>
       <c r="E14" t="n">
-        <v>-27.5187</v>
+        <v>-23.2531</v>
       </c>
       <c r="F14" t="n">
-        <v>-12.0827</v>
+        <v>-5.6429</v>
       </c>
       <c r="G14" t="n">
         <v>-19.349</v>
@@ -1546,13 +1546,13 @@
         <v>29.1059</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.9881</v>
+        <v>6.717</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3267999999999996</v>
+        <v>4.592000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.3152</v>
+        <v>2.1247</v>
       </c>
       <c r="V14" t="n">
         <v>-17.2403</v>
@@ -1579,19 +1579,19 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>226.0244</v>
+        <v>252.1622</v>
       </c>
       <c r="E15" t="n">
-        <v>187.1013</v>
+        <v>194.3634</v>
       </c>
       <c r="F15" t="n">
-        <v>38.92409999999998</v>
+        <v>57.7978</v>
       </c>
       <c r="G15" t="n">
         <v>119.6041</v>
       </c>
       <c r="H15" t="n">
-        <v>74.39400000000002</v>
+        <v>74.39400000000001</v>
       </c>
       <c r="I15" t="n">
         <v>45.2102</v>
@@ -1624,13 +1624,13 @@
         <v>360.4078999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>81.43819999999999</v>
+        <v>107.5767</v>
       </c>
       <c r="T15" t="n">
-        <v>64.52170000000002</v>
+        <v>71.7846</v>
       </c>
       <c r="U15" t="n">
-        <v>16.9172</v>
+        <v>35.79089999999999</v>
       </c>
       <c r="V15" t="n">
         <v>46.46969999999999</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SA TINTINA CB ES CASTELL MENORCA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SA TINTINA CB ES CASTELL MENORCA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>48.2062</v>
+        <v>42.2648</v>
       </c>
       <c r="E3" t="n">
-        <v>27.8215</v>
+        <v>37.88200000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>20.3846</v>
+        <v>4.382400000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>9.626799999999999</v>
+        <v>21.0398</v>
       </c>
       <c r="H3" t="n">
-        <v>23.362</v>
+        <v>5.840300000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-13.7348</v>
+        <v>15.1992</v>
       </c>
       <c r="J3" t="n">
-        <v>38.8128</v>
+        <v>49.3152</v>
       </c>
       <c r="K3" t="n">
-        <v>39.9804</v>
+        <v>24.1129</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.167399999999998</v>
+        <v>25.2023</v>
       </c>
       <c r="M3" t="n">
-        <v>-29.1857</v>
+        <v>-28.2757</v>
       </c>
       <c r="N3" t="n">
-        <v>-16.6188</v>
+        <v>-18.2722</v>
       </c>
       <c r="O3" t="n">
-        <v>-12.5673</v>
+        <v>-10.0033</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3905999999999994</v>
+        <v>-1.5628</v>
       </c>
       <c r="Q3" t="n">
-        <v>-50.7891</v>
+        <v>-47.8589</v>
       </c>
       <c r="R3" t="n">
-        <v>51.18</v>
+        <v>46.2965</v>
       </c>
       <c r="S3" t="n">
-        <v>28.9952</v>
+        <v>8.0067</v>
       </c>
       <c r="T3" t="n">
-        <v>16.4156</v>
+        <v>6.6184</v>
       </c>
       <c r="U3" t="n">
-        <v>12.5794</v>
+        <v>1.3884</v>
       </c>
       <c r="V3" t="n">
-        <v>9.193300000000001</v>
+        <v>14.7812</v>
       </c>
       <c r="W3" t="n">
-        <v>23.3819</v>
+        <v>29.8072</v>
       </c>
       <c r="X3" t="n">
-        <v>-14.1888</v>
+        <v>-15.0262</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>J. GASCON TORNE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>42.2648</v>
+        <v>33.2327</v>
       </c>
       <c r="E4" t="n">
-        <v>37.88200000000001</v>
+        <v>12.6151</v>
       </c>
       <c r="F4" t="n">
-        <v>4.382400000000001</v>
+        <v>20.6175</v>
       </c>
       <c r="G4" t="n">
-        <v>21.0398</v>
+        <v>29.8904</v>
       </c>
       <c r="H4" t="n">
-        <v>5.840300000000001</v>
+        <v>18.5981</v>
       </c>
       <c r="I4" t="n">
-        <v>15.1992</v>
+        <v>11.292</v>
       </c>
       <c r="J4" t="n">
-        <v>49.3152</v>
+        <v>41.0762</v>
       </c>
       <c r="K4" t="n">
-        <v>24.1129</v>
+        <v>30.0379</v>
       </c>
       <c r="L4" t="n">
-        <v>25.2023</v>
+        <v>11.0382</v>
       </c>
       <c r="M4" t="n">
-        <v>-28.2757</v>
+        <v>-11.1857</v>
       </c>
       <c r="N4" t="n">
-        <v>-18.2722</v>
+        <v>-11.4399</v>
       </c>
       <c r="O4" t="n">
-        <v>-10.0033</v>
+        <v>0.2539000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5628</v>
+        <v>-14.0649</v>
       </c>
       <c r="Q4" t="n">
-        <v>-47.8589</v>
+        <v>-50.7891</v>
       </c>
       <c r="R4" t="n">
-        <v>46.2965</v>
+        <v>36.7245</v>
       </c>
       <c r="S4" t="n">
-        <v>8.0067</v>
+        <v>12.5243</v>
       </c>
       <c r="T4" t="n">
-        <v>6.6184</v>
+        <v>6.4249</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3884</v>
+        <v>6.0992</v>
       </c>
       <c r="V4" t="n">
-        <v>14.7812</v>
+        <v>4.8824</v>
       </c>
       <c r="W4" t="n">
-        <v>29.8072</v>
+        <v>15.9029</v>
       </c>
       <c r="X4" t="n">
-        <v>-15.0262</v>
+        <v>-11.0206</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>33.2327</v>
+        <v>31.7196</v>
       </c>
       <c r="E5" t="n">
-        <v>12.6151</v>
+        <v>11.3353</v>
       </c>
       <c r="F5" t="n">
-        <v>20.6175</v>
+        <v>20.3846</v>
       </c>
       <c r="G5" t="n">
-        <v>29.8904</v>
+        <v>-6.8594</v>
       </c>
       <c r="H5" t="n">
-        <v>18.5981</v>
+        <v>14.7663</v>
       </c>
       <c r="I5" t="n">
-        <v>11.292</v>
+        <v>-21.6258</v>
       </c>
       <c r="J5" t="n">
-        <v>41.0762</v>
+        <v>22.3261</v>
       </c>
       <c r="K5" t="n">
-        <v>30.0379</v>
+        <v>31.3846</v>
       </c>
       <c r="L5" t="n">
-        <v>11.0382</v>
+        <v>-9.058299999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-11.1857</v>
+        <v>-29.1857</v>
       </c>
       <c r="N5" t="n">
-        <v>-11.4399</v>
+        <v>-16.6188</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2539000000000001</v>
+        <v>-12.5673</v>
       </c>
       <c r="P5" t="n">
-        <v>-14.0649</v>
+        <v>0.3905999999999994</v>
       </c>
       <c r="Q5" t="n">
         <v>-50.7891</v>
       </c>
       <c r="R5" t="n">
-        <v>36.7245</v>
+        <v>51.18</v>
       </c>
       <c r="S5" t="n">
-        <v>12.5243</v>
+        <v>28.9952</v>
       </c>
       <c r="T5" t="n">
-        <v>6.4249</v>
+        <v>16.4156</v>
       </c>
       <c r="U5" t="n">
-        <v>6.0992</v>
+        <v>12.5794</v>
       </c>
       <c r="V5" t="n">
-        <v>4.8824</v>
+        <v>9.193300000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>15.9029</v>
+        <v>23.3819</v>
       </c>
       <c r="X5" t="n">
-        <v>-11.0206</v>
+        <v>-14.1888</v>
       </c>
     </row>
     <row r="6">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>6.281700000000001</v>
+        <v>16.4869</v>
       </c>
       <c r="E8" t="n">
-        <v>8.0853</v>
+        <v>16.4869</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8034</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4.366300000000001</v>
+        <v>16.4869</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3322999999999998</v>
+        <v>8.596</v>
       </c>
       <c r="I8" t="n">
-        <v>4.0339</v>
+        <v>7.891</v>
       </c>
       <c r="J8" t="n">
-        <v>12.7318</v>
+        <v>16.4869</v>
       </c>
       <c r="K8" t="n">
-        <v>6.127</v>
+        <v>8.596</v>
       </c>
       <c r="L8" t="n">
-        <v>6.6051</v>
+        <v>7.891</v>
       </c>
       <c r="M8" t="n">
-        <v>-8.365599999999999</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-5.7944</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.5711</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>11.33</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-6.6414</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>17.9716</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6625</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.382</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2805000000000002</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-12.0764</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.387</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-11.6894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ RODRIGUEZ</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5211</v>
+        <v>6.281700000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.2112</v>
+        <v>8.0853</v>
       </c>
       <c r="F9" t="n">
-        <v>8.7323</v>
+        <v>-1.8034</v>
       </c>
       <c r="G9" t="n">
-        <v>4.121</v>
+        <v>4.366300000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0411</v>
+        <v>0.3322999999999998</v>
       </c>
       <c r="I9" t="n">
-        <v>6.162</v>
+        <v>4.0339</v>
       </c>
       <c r="J9" t="n">
-        <v>9.798999999999999</v>
+        <v>12.7318</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8779</v>
+        <v>6.127</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9214</v>
+        <v>6.6051</v>
       </c>
       <c r="M9" t="n">
-        <v>-5.6782</v>
+        <v>-8.365599999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.9186</v>
+        <v>-5.7944</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7595</v>
+        <v>-2.5711</v>
       </c>
       <c r="P9" t="n">
-        <v>-5.2743</v>
+        <v>11.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>-21.2922</v>
+        <v>-6.6414</v>
       </c>
       <c r="R9" t="n">
-        <v>16.018</v>
+        <v>17.9716</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9993999999999998</v>
+        <v>2.6625</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1739</v>
+        <v>2.382</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1746</v>
+        <v>0.2805000000000002</v>
       </c>
       <c r="V9" t="n">
-        <v>1.675</v>
+        <v>-12.0764</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1081</v>
+        <v>-0.387</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.4331999999999999</v>
+        <v>-11.6894</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>V. FERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8759999999999994</v>
+        <v>1.5211</v>
       </c>
       <c r="E10" t="n">
-        <v>5.5645</v>
+        <v>-7.2112</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.688499999999999</v>
+        <v>8.7323</v>
       </c>
       <c r="G10" t="n">
-        <v>2.9581</v>
+        <v>4.121</v>
       </c>
       <c r="H10" t="n">
-        <v>1.189399999999999</v>
+        <v>-2.0411</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7689</v>
+        <v>6.162</v>
       </c>
       <c r="J10" t="n">
-        <v>26.0902</v>
+        <v>9.798999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>14.7271</v>
+        <v>1.8779</v>
       </c>
       <c r="L10" t="n">
-        <v>11.3631</v>
+        <v>7.9214</v>
       </c>
       <c r="M10" t="n">
-        <v>-23.1321</v>
+        <v>-5.6782</v>
       </c>
       <c r="N10" t="n">
-        <v>-13.5379</v>
+        <v>-3.9186</v>
       </c>
       <c r="O10" t="n">
-        <v>-9.594199999999999</v>
+        <v>-1.7595</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.4929</v>
+        <v>-5.2743</v>
       </c>
       <c r="Q10" t="n">
-        <v>-39.0682</v>
+        <v>-21.2922</v>
       </c>
       <c r="R10" t="n">
-        <v>34.5757</v>
+        <v>16.018</v>
       </c>
       <c r="S10" t="n">
-        <v>11.3871</v>
+        <v>0.9993999999999998</v>
       </c>
       <c r="T10" t="n">
-        <v>7.0723</v>
+        <v>2.1739</v>
       </c>
       <c r="U10" t="n">
-        <v>4.3146</v>
+        <v>-1.1746</v>
       </c>
       <c r="V10" t="n">
-        <v>-8.9765</v>
+        <v>1.675</v>
       </c>
       <c r="W10" t="n">
-        <v>11.4701</v>
+        <v>2.1081</v>
       </c>
       <c r="X10" t="n">
-        <v>-20.4465</v>
+        <v>-0.4331999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. MAS CARDONA</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3088</v>
+        <v>0.8759999999999994</v>
       </c>
       <c r="E11" t="n">
-        <v>0.352</v>
+        <v>5.5645</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6608</v>
+        <v>-4.688499999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7109000000000001</v>
+        <v>2.9581</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1384</v>
+        <v>1.189399999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8492999999999999</v>
+        <v>1.7689</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0417</v>
+        <v>26.0902</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0013</v>
+        <v>14.7271</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0405</v>
+        <v>11.3631</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6692</v>
+        <v>-23.1321</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1397</v>
+        <v>-13.5379</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8089</v>
+        <v>-9.594199999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-4.4929</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-39.0682</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>34.5757</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4175</v>
+        <v>11.3871</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3103</v>
+        <v>7.0723</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1073</v>
+        <v>4.3146</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4372</v>
+        <v>-8.9765</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>11.4701</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4372</v>
+        <v>-20.4465</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. TALTAVULL BALLE</t>
+          <t>O. MAS CARDONA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3225</v>
+        <v>-1.3088</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0154</v>
+        <v>0.352</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3071000000000002</v>
+        <v>-1.6608</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.2712</v>
+        <v>0.7109000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5464</v>
+        <v>-0.1384</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.8177</v>
+        <v>0.8492999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.8505</v>
+        <v>0.0417</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0451</v>
+        <v>0.0013</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.8956</v>
+        <v>0.0405</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5791999999999999</v>
+        <v>0.6692</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4985999999999999</v>
+        <v>-0.1397</v>
       </c>
       <c r="O12" t="n">
-        <v>1.078</v>
+        <v>0.8089</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9301</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.9301</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2584</v>
+        <v>0.4175</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1648999999999999</v>
+        <v>0.3103</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.09380000000000002</v>
+        <v>0.1073</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.7229</v>
+        <v>-2.4372</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.7229</v>
+        <v>-2.4372</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. NDOYE</t>
+          <t>P. TALTAVULL BALLE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.673999999999998</v>
+        <v>-3.3225</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.908999999999999</v>
+        <v>-3.0154</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2345</v>
+        <v>-0.3071000000000002</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.7758</v>
+        <v>-2.2712</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.6923</v>
+        <v>0.5464</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.0835</v>
+        <v>-2.8177</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3506</v>
+        <v>-2.8505</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1646999999999994</v>
+        <v>1.0451</v>
       </c>
       <c r="L13" t="n">
-        <v>2.1862</v>
+        <v>-3.8956</v>
       </c>
       <c r="M13" t="n">
-        <v>-12.1262</v>
+        <v>0.5791999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.8568</v>
+        <v>-0.4985999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.2695</v>
+        <v>1.078</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.664800000000001</v>
+        <v>2.9301</v>
       </c>
       <c r="Q13" t="n">
-        <v>-28.7153</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>23.0506</v>
+        <v>2.9301</v>
       </c>
       <c r="S13" t="n">
-        <v>5.466699999999999</v>
+        <v>-0.2584</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9938</v>
+        <v>-0.1648999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4731</v>
+        <v>-0.09380000000000002</v>
       </c>
       <c r="V13" t="n">
-        <v>3.2996</v>
+        <v>-3.7229</v>
       </c>
       <c r="W13" t="n">
-        <v>14.4617</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-11.1623</v>
+        <v>-3.7229</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>S. NDOYE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,147 +1498,225 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D14" t="n">
-        <v>-28.896</v>
+        <v>-6.673999999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-23.2531</v>
+        <v>-8.908999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.6429</v>
+        <v>2.2345</v>
       </c>
       <c r="G14" t="n">
-        <v>-19.349</v>
+        <v>-9.7758</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.2439</v>
+        <v>-6.6923</v>
       </c>
       <c r="I14" t="n">
-        <v>-15.1052</v>
+        <v>-3.0835</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.7700000000000006</v>
+        <v>2.3506</v>
       </c>
       <c r="K14" t="n">
-        <v>4.342499999999999</v>
+        <v>0.1646999999999994</v>
       </c>
       <c r="L14" t="n">
-        <v>-5.1124</v>
+        <v>2.1862</v>
       </c>
       <c r="M14" t="n">
-        <v>-18.5793</v>
+        <v>-12.1262</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.5863</v>
+        <v>-6.8568</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.992799999999999</v>
+        <v>-5.2695</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9765000000000001</v>
+        <v>-5.664800000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-28.1291</v>
+        <v>-28.7153</v>
       </c>
       <c r="R14" t="n">
-        <v>29.1059</v>
+        <v>23.0506</v>
       </c>
       <c r="S14" t="n">
-        <v>6.717</v>
+        <v>5.466699999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>4.592000000000001</v>
+        <v>2.9938</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1247</v>
+        <v>2.4731</v>
       </c>
       <c r="V14" t="n">
-        <v>-17.2403</v>
+        <v>3.2996</v>
       </c>
       <c r="W14" t="n">
-        <v>1.054</v>
+        <v>14.4617</v>
       </c>
       <c r="X14" t="n">
-        <v>-18.2944</v>
+        <v>-11.1623</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>L. ANDUJAR MASCARO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>25</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-28.896</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-23.2531</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-5.6429</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-19.349</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-4.2439</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-15.1052</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.7700000000000006</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.342499999999999</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-5.1124</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-18.5793</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-8.5863</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-9.992799999999999</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.9765000000000001</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-28.1291</v>
+      </c>
+      <c r="R15" t="n">
+        <v>29.1059</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6.717</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4.592000000000001</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.1247</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-17.2403</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-18.2944</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>SA TINTINA CB ES CASTELL MENORCA</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C16" t="n">
         <v>26</v>
       </c>
-      <c r="D15" t="n">
-        <v>252.1622</v>
-      </c>
-      <c r="E15" t="n">
-        <v>194.3634</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="D16" t="n">
+        <v>252.1625</v>
+      </c>
+      <c r="E16" t="n">
+        <v>194.3641000000001</v>
+      </c>
+      <c r="F16" t="n">
         <v>57.7978</v>
       </c>
-      <c r="G15" t="n">
-        <v>119.6041</v>
-      </c>
-      <c r="H15" t="n">
-        <v>74.39400000000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>45.2102</v>
-      </c>
-      <c r="J15" t="n">
-        <v>307.505</v>
-      </c>
-      <c r="K15" t="n">
-        <v>198.0659</v>
-      </c>
-      <c r="L15" t="n">
-        <v>109.44</v>
-      </c>
-      <c r="M15" t="n">
+      <c r="G16" t="n">
+        <v>119.6048</v>
+      </c>
+      <c r="H16" t="n">
+        <v>74.39429999999999</v>
+      </c>
+      <c r="I16" t="n">
+        <v>45.21019999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>307.5051999999999</v>
+      </c>
+      <c r="K16" t="n">
+        <v>198.0661</v>
+      </c>
+      <c r="L16" t="n">
+        <v>109.4401</v>
+      </c>
+      <c r="M16" t="n">
         <v>-187.9011</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N16" t="n">
         <v>-123.6714</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O16" t="n">
         <v>-64.22959999999999</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P16" t="n">
         <v>-21.488</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q16" t="n">
         <v>-381.8937</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R16" t="n">
         <v>360.4078999999999</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S16" t="n">
         <v>107.5767</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>71.7846</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>35.79089999999999</v>
       </c>
-      <c r="V15" t="n">
+      <c r="V16" t="n">
         <v>46.46969999999999</v>
       </c>
-      <c r="W15" t="n">
+      <c r="W16" t="n">
         <v>196.9674</v>
       </c>
-      <c r="X15" t="n">
+      <c r="X16" t="n">
         <v>-150.4987</v>
       </c>
     </row>
